--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/91.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/91.xlsx
@@ -426,13 +426,13 @@
         <v>-1.339116552596658</v>
       </c>
       <c r="E2">
-        <v>-5.978546230419583</v>
+        <v>-5.691646545311752</v>
       </c>
       <c r="F2">
-        <v>0.6208637062529301</v>
+        <v>-0.8376659741434378</v>
       </c>
       <c r="G2">
-        <v>-9.485954564775072</v>
+        <v>-8.882347804565089</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.212217088589756</v>
       </c>
       <c r="E3">
-        <v>-7.281200962452054</v>
+        <v>-6.524195134275557</v>
       </c>
       <c r="F3">
-        <v>0.756389583555346</v>
+        <v>-1.073348097383536</v>
       </c>
       <c r="G3">
-        <v>-9.200387405282214</v>
+        <v>-8.27607547412758</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-1.077643791349991</v>
       </c>
       <c r="E4">
-        <v>-8.25823562019532</v>
+        <v>-7.289839642007698</v>
       </c>
       <c r="F4">
-        <v>0.607415989835883</v>
+        <v>-0.7714976427426189</v>
       </c>
       <c r="G4">
-        <v>-8.509776276201086</v>
+        <v>-8.166467278586575</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-0.9624103659857506</v>
       </c>
       <c r="E5">
-        <v>-7.489347454418486</v>
+        <v>-8.429306394665007</v>
       </c>
       <c r="F5">
-        <v>1.091114626943765</v>
+        <v>-0.6327759240002025</v>
       </c>
       <c r="G5">
-        <v>-9.088853785605263</v>
+        <v>-7.79574415739308</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-0.867146675025768</v>
       </c>
       <c r="E6">
-        <v>-9.868360893027498</v>
+        <v>-9.822434682197544</v>
       </c>
       <c r="F6">
-        <v>1.341144073600351</v>
+        <v>-0.6080673811094989</v>
       </c>
       <c r="G6">
-        <v>-8.519442558049683</v>
+        <v>-7.630426588394604</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-0.7912461675968631</v>
       </c>
       <c r="E7">
-        <v>-9.459568608747274</v>
+        <v>-10.6434498033123</v>
       </c>
       <c r="F7">
-        <v>0.9632793126089394</v>
+        <v>-0.3727298587089649</v>
       </c>
       <c r="G7">
-        <v>-8.349870780739987</v>
+        <v>-7.468850216395194</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-0.7211154579719589</v>
       </c>
       <c r="E8">
-        <v>-10.98938738740257</v>
+        <v>-11.44017694459946</v>
       </c>
       <c r="F8">
-        <v>1.264243414128861</v>
+        <v>-0.2858970740779095</v>
       </c>
       <c r="G8">
-        <v>-7.217036068348545</v>
+        <v>-7.366561243315376</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-0.6409134605746739</v>
       </c>
       <c r="E9">
-        <v>-12.15501521819497</v>
+        <v>-12.71890917940092</v>
       </c>
       <c r="F9">
-        <v>1.285775996397232</v>
+        <v>0.03072896992674271</v>
       </c>
       <c r="G9">
-        <v>-7.25961209114042</v>
+        <v>-6.638643879399534</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.5311039094903083</v>
       </c>
       <c r="E10">
-        <v>-12.88284058360323</v>
+        <v>-13.24076018236562</v>
       </c>
       <c r="F10">
-        <v>1.48879393621014</v>
+        <v>0.08105643148382667</v>
       </c>
       <c r="G10">
-        <v>-6.926888357470578</v>
+        <v>-6.339476045959271</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-0.3797393763572364</v>
       </c>
       <c r="E11">
-        <v>-14.0734042951899</v>
+        <v>-14.1405326498331</v>
       </c>
       <c r="F11">
-        <v>1.952581934424333</v>
+        <v>-0.0284015520198916</v>
       </c>
       <c r="G11">
-        <v>-6.128467835871723</v>
+        <v>-5.448019030111502</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-0.1847804377047826</v>
       </c>
       <c r="E12">
-        <v>-14.92477939108915</v>
+        <v>-15.02231755905275</v>
       </c>
       <c r="F12">
-        <v>2.098198983427652</v>
+        <v>-0.002547377011116232</v>
       </c>
       <c r="G12">
-        <v>-5.384831178772787</v>
+        <v>-4.797191732482053</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>0.04797288799082183</v>
       </c>
       <c r="E13">
-        <v>-15.76560948343466</v>
+        <v>-16.83816384843766</v>
       </c>
       <c r="F13">
-        <v>2.345494817655</v>
+        <v>0.1572148737624076</v>
       </c>
       <c r="G13">
-        <v>-5.170397671781697</v>
+        <v>-4.845433071036645</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>0.3035603325943406</v>
       </c>
       <c r="E14">
-        <v>-17.28314721620244</v>
+        <v>-17.68845910939246</v>
       </c>
       <c r="F14">
-        <v>2.196998363559549</v>
+        <v>0.3734535573239962</v>
       </c>
       <c r="G14">
-        <v>-5.239263892606083</v>
+        <v>-3.81450224689783</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>0.5649822283617308</v>
       </c>
       <c r="E15">
-        <v>-17.22817531110701</v>
+        <v>-18.9397552301821</v>
       </c>
       <c r="F15">
-        <v>2.554261627243337</v>
+        <v>0.1316083806070693</v>
       </c>
       <c r="G15">
-        <v>-3.773826846168285</v>
+        <v>-2.911182007628042</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>0.8182511356767697</v>
       </c>
       <c r="E16">
-        <v>-18.78508964044548</v>
+        <v>-19.99314252492101</v>
       </c>
       <c r="F16">
-        <v>3.056547172135234</v>
+        <v>0.469626184421616</v>
       </c>
       <c r="G16">
-        <v>-3.3008356378517</v>
+        <v>-2.40907055414218</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>1.050683236118894</v>
       </c>
       <c r="E17">
-        <v>-19.94332890829102</v>
+        <v>-20.36705614049533</v>
       </c>
       <c r="F17">
-        <v>3.006005163420825</v>
+        <v>0.5889533371622876</v>
       </c>
       <c r="G17">
-        <v>-3.190938955033378</v>
+        <v>-1.806134755292113</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>1.254571948265569</v>
       </c>
       <c r="E18">
-        <v>-19.83402884585551</v>
+        <v>-21.2131317387441</v>
       </c>
       <c r="F18">
-        <v>2.78490893340922</v>
+        <v>0.8144498548175634</v>
       </c>
       <c r="G18">
-        <v>-1.707430334535893</v>
+        <v>-1.343646572465577</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.425797748204465</v>
       </c>
       <c r="E19">
-        <v>-21.17835690032131</v>
+        <v>-21.9446783814994</v>
       </c>
       <c r="F19">
-        <v>3.69218164479499</v>
+        <v>0.8765277079833583</v>
       </c>
       <c r="G19">
-        <v>-1.859514039202015</v>
+        <v>-0.9193535830070277</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.561676227809173</v>
       </c>
       <c r="E20">
-        <v>-21.49389297751383</v>
+        <v>-22.69887248560899</v>
       </c>
       <c r="F20">
-        <v>3.837376226422882</v>
+        <v>1.479186531072471</v>
       </c>
       <c r="G20">
-        <v>-1.786535895646626</v>
+        <v>0.01784628882163734</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.662260896815817</v>
       </c>
       <c r="E21">
-        <v>-23.07417742697712</v>
+        <v>-23.56938142608173</v>
       </c>
       <c r="F21">
-        <v>4.485625077892468</v>
+        <v>1.527081077567533</v>
       </c>
       <c r="G21">
-        <v>-1.621163501011737</v>
+        <v>0.3065032645380778</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.727814685347935</v>
       </c>
       <c r="E22">
-        <v>-22.76151537202137</v>
+        <v>-24.57397264096523</v>
       </c>
       <c r="F22">
-        <v>3.508578980168896</v>
+        <v>1.736280294940132</v>
       </c>
       <c r="G22">
-        <v>-0.9010548741679147</v>
+        <v>0.06782116178472786</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.75929558246973</v>
       </c>
       <c r="E23">
-        <v>-23.83637892252098</v>
+        <v>-24.01906207585489</v>
       </c>
       <c r="F23">
-        <v>4.434839529161636</v>
+        <v>2.203295612555631</v>
       </c>
       <c r="G23">
-        <v>-1.283043358272064</v>
+        <v>-0.04286135515551989</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.757845500070223</v>
       </c>
       <c r="E24">
-        <v>-23.24167643970745</v>
+        <v>-24.83366048547278</v>
       </c>
       <c r="F24">
-        <v>4.787521921107943</v>
+        <v>2.346225437704269</v>
       </c>
       <c r="G24">
-        <v>-1.381395328508484</v>
+        <v>0.1540749415859286</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.723108683688578</v>
       </c>
       <c r="E25">
-        <v>-23.86908961491533</v>
+        <v>-24.98270262707558</v>
       </c>
       <c r="F25">
-        <v>4.858130301787766</v>
+        <v>2.673480263854242</v>
       </c>
       <c r="G25">
-        <v>-1.152644498179729</v>
+        <v>0.02909859800933561</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.655433882898842</v>
       </c>
       <c r="E26">
-        <v>-23.7807632696702</v>
+        <v>-25.00428271311939</v>
       </c>
       <c r="F26">
-        <v>4.872596910110257</v>
+        <v>2.745564795245855</v>
       </c>
       <c r="G26">
-        <v>-1.196424074228107</v>
+        <v>-0.1985400551236051</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.557183585976347</v>
       </c>
       <c r="E27">
-        <v>-24.52608611438995</v>
+        <v>-25.51802664757803</v>
       </c>
       <c r="F27">
-        <v>4.613023014238616</v>
+        <v>2.734342073672727</v>
       </c>
       <c r="G27">
-        <v>-1.577049749655696</v>
+        <v>-0.6089882660154803</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.433882980277563</v>
       </c>
       <c r="E28">
-        <v>-24.39999046535683</v>
+        <v>-25.24639001408894</v>
       </c>
       <c r="F28">
-        <v>5.089453555754335</v>
+        <v>2.813707954534948</v>
       </c>
       <c r="G28">
-        <v>-1.190226166568805</v>
+        <v>-0.9448683898959779</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.293702809923793</v>
       </c>
       <c r="E29">
-        <v>-24.0677086401026</v>
+        <v>-25.77516857354346</v>
       </c>
       <c r="F29">
-        <v>4.763868718288405</v>
+        <v>2.895479414334898</v>
       </c>
       <c r="G29">
-        <v>-2.039752013538703</v>
+        <v>-1.091720162401509</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.14667612272083</v>
       </c>
       <c r="E30">
-        <v>-23.22189054095597</v>
+        <v>-25.09005483339975</v>
       </c>
       <c r="F30">
-        <v>5.154521815244236</v>
+        <v>2.93987659365534</v>
       </c>
       <c r="G30">
-        <v>-1.859529703669562</v>
+        <v>-1.501131907690712</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.001964242081063</v>
       </c>
       <c r="E31">
-        <v>-22.78179134970919</v>
+        <v>-24.42890927581162</v>
       </c>
       <c r="F31">
-        <v>5.232444680090779</v>
+        <v>3.137488607797579</v>
       </c>
       <c r="G31">
-        <v>-2.07794720690669</v>
+        <v>-1.962557517468666</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.8658212719442008</v>
       </c>
       <c r="E32">
-        <v>-23.30574387760426</v>
+        <v>-25.07339630277586</v>
       </c>
       <c r="F32">
-        <v>4.981785674208066</v>
+        <v>2.957144740534099</v>
       </c>
       <c r="G32">
-        <v>-3.290593686820763</v>
+        <v>-2.41488729309118</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.7437231955438911</v>
       </c>
       <c r="E33">
-        <v>-23.0031325940546</v>
+        <v>-24.74310386574622</v>
       </c>
       <c r="F33">
-        <v>5.3251257385856</v>
+        <v>3.205427988705583</v>
       </c>
       <c r="G33">
-        <v>-2.750493288789611</v>
+        <v>-2.681355550527749</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.6399149374198495</v>
       </c>
       <c r="E34">
-        <v>-22.32961877314113</v>
+        <v>-24.15141661435452</v>
       </c>
       <c r="F34">
-        <v>5.280554602110569</v>
+        <v>3.190248984416685</v>
       </c>
       <c r="G34">
-        <v>-2.643512807679562</v>
+        <v>-2.342739366315764</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.5576226986598055</v>
       </c>
       <c r="E35">
-        <v>-21.4431365819131</v>
+        <v>-24.03333666317832</v>
       </c>
       <c r="F35">
-        <v>4.965758421698701</v>
+        <v>3.329779189744234</v>
       </c>
       <c r="G35">
-        <v>-3.085835599284339</v>
+        <v>-3.168272470493332</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.498982487374182</v>
       </c>
       <c r="E36">
-        <v>-21.78029427726268</v>
+        <v>-23.25154446981525</v>
       </c>
       <c r="F36">
-        <v>4.763698074603429</v>
+        <v>3.413288564355258</v>
       </c>
       <c r="G36">
-        <v>-2.922353383733416</v>
+        <v>-3.297812395615191</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.461370896783985</v>
       </c>
       <c r="E37">
-        <v>-21.44160820014557</v>
+        <v>-22.57422215411691</v>
       </c>
       <c r="F37">
-        <v>5.133817600378665</v>
+        <v>3.050370864779961</v>
       </c>
       <c r="G37">
-        <v>-3.540277467281064</v>
+        <v>-3.547783357980515</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.437885169516839</v>
       </c>
       <c r="E38">
-        <v>-20.85057715614319</v>
+        <v>-22.59527893553379</v>
       </c>
       <c r="F38">
-        <v>5.146766639619226</v>
+        <v>3.439037536703878</v>
       </c>
       <c r="G38">
-        <v>-4.020790230764646</v>
+        <v>-3.731222105185908</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.4198195875405147</v>
       </c>
       <c r="E39">
-        <v>-20.26044320578698</v>
+        <v>-21.82146921433704</v>
       </c>
       <c r="F39">
-        <v>4.609858650759922</v>
+        <v>3.348385978345917</v>
       </c>
       <c r="G39">
-        <v>-3.356841330820262</v>
+        <v>-3.393412641052577</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.3972940151971616</v>
       </c>
       <c r="E40">
-        <v>-20.46694087285745</v>
+        <v>-21.30902108181174</v>
       </c>
       <c r="F40">
-        <v>4.79084698786278</v>
+        <v>3.417622582606705</v>
       </c>
       <c r="G40">
-        <v>-3.768174584128525</v>
+        <v>-3.992883981830237</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.3630061360401112</v>
       </c>
       <c r="E41">
-        <v>-18.85122537758205</v>
+        <v>-20.27706020429762</v>
       </c>
       <c r="F41">
-        <v>5.053522291290503</v>
+        <v>3.066643314040554</v>
       </c>
       <c r="G41">
-        <v>-3.39754544974031</v>
+        <v>-3.854796478917073</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.3124623101812798</v>
       </c>
       <c r="E42">
-        <v>-18.97076310593327</v>
+        <v>-20.03818410173878</v>
       </c>
       <c r="F42">
-        <v>4.674676743294177</v>
+        <v>3.152530103097613</v>
       </c>
       <c r="G42">
-        <v>-3.635854216017131</v>
+        <v>-3.792699918817443</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.2407296298871993</v>
       </c>
       <c r="E43">
-        <v>-17.9738553320007</v>
+        <v>-19.43600999175189</v>
       </c>
       <c r="F43">
-        <v>5.273356089380242</v>
+        <v>3.076772590641987</v>
       </c>
       <c r="G43">
-        <v>-4.548306839866632</v>
+        <v>-3.818115517411931</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.1459096398126299</v>
       </c>
       <c r="E44">
-        <v>-17.52954063125922</v>
+        <v>-18.42911374458311</v>
       </c>
       <c r="F44">
-        <v>4.569691115398173</v>
+        <v>3.150031747010769</v>
       </c>
       <c r="G44">
-        <v>-4.222861862116815</v>
+        <v>-4.262414642672181</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.02739446781415861</v>
       </c>
       <c r="E45">
-        <v>-17.51105884086373</v>
+        <v>-18.48684338199822</v>
       </c>
       <c r="F45">
-        <v>4.641235551243161</v>
+        <v>3.101192861676516</v>
       </c>
       <c r="G45">
-        <v>-3.608159437394601</v>
+        <v>-4.278575151691173</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.1169447707607559</v>
       </c>
       <c r="E46">
-        <v>-16.04906615635421</v>
+        <v>-18.17224177735379</v>
       </c>
       <c r="F46">
-        <v>5.030193808492863</v>
+        <v>2.889288196366375</v>
       </c>
       <c r="G46">
-        <v>-4.15392776193306</v>
+        <v>-4.407436283219342</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.2864939401763328</v>
       </c>
       <c r="E47">
-        <v>-16.38393127905249</v>
+        <v>-16.50924197114522</v>
       </c>
       <c r="F47">
-        <v>4.524147475592256</v>
+        <v>2.942591982001717</v>
       </c>
       <c r="G47">
-        <v>-3.680427458421208</v>
+        <v>-4.550431985963799</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.4799536924422368</v>
       </c>
       <c r="E48">
-        <v>-15.1294828708673</v>
+        <v>-16.51892310674339</v>
       </c>
       <c r="F48">
-        <v>5.051308893590223</v>
+        <v>2.912079897087</v>
       </c>
       <c r="G48">
-        <v>-4.704828810337648</v>
+        <v>-4.347081089761985</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.6941701518971248</v>
       </c>
       <c r="E49">
-        <v>-14.9491753544112</v>
+        <v>-16.15938790877563</v>
       </c>
       <c r="F49">
-        <v>4.651497366629042</v>
+        <v>2.755940925333321</v>
       </c>
       <c r="G49">
-        <v>-4.135091239708178</v>
+        <v>-4.721743824543471</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.9218431938167732</v>
       </c>
       <c r="E50">
-        <v>-13.87344793595603</v>
+        <v>-14.87342493305765</v>
       </c>
       <c r="F50">
-        <v>4.470018636023726</v>
+        <v>2.752180137324612</v>
       </c>
       <c r="G50">
-        <v>-4.004909071416905</v>
+        <v>-4.714595605853003</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.157411251843517</v>
       </c>
       <c r="E51">
-        <v>-14.50682096941503</v>
+        <v>-14.98328152581069</v>
       </c>
       <c r="F51">
-        <v>4.23368044580061</v>
+        <v>2.989113095342938</v>
       </c>
       <c r="G51">
-        <v>-5.008609829470407</v>
+        <v>-4.807551167019591</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.394800150136217</v>
       </c>
       <c r="E52">
-        <v>-13.5187013906458</v>
+        <v>-13.54313057965844</v>
       </c>
       <c r="F52">
-        <v>4.285420273779467</v>
+        <v>2.926917614005945</v>
       </c>
       <c r="G52">
-        <v>-4.9222698950977</v>
+        <v>-4.961070781210825</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.627440375726457</v>
       </c>
       <c r="E53">
-        <v>-13.41315167803661</v>
+        <v>-12.78453822475586</v>
       </c>
       <c r="F53">
-        <v>4.135267084878418</v>
+        <v>2.834556305328606</v>
       </c>
       <c r="G53">
-        <v>-4.791497698528835</v>
+        <v>-4.934237548303363</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.85476721053487</v>
       </c>
       <c r="E54">
-        <v>-12.76807904827556</v>
+        <v>-12.27725668711865</v>
       </c>
       <c r="F54">
-        <v>4.085094528025657</v>
+        <v>2.57354602038051</v>
       </c>
       <c r="G54">
-        <v>-4.886740271957239</v>
+        <v>-5.021608726789561</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.075476048649975</v>
       </c>
       <c r="E55">
-        <v>-12.31517135330301</v>
+        <v>-11.91746814326008</v>
       </c>
       <c r="F55">
-        <v>4.323086139584761</v>
+        <v>2.64176538947066</v>
       </c>
       <c r="G55">
-        <v>-5.47069073614073</v>
+        <v>-5.463939350628111</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.290256874598422</v>
       </c>
       <c r="E56">
-        <v>-10.53179487005561</v>
+        <v>-11.44739522588201</v>
       </c>
       <c r="F56">
-        <v>3.675915822473619</v>
+        <v>2.521337336451668</v>
       </c>
       <c r="G56">
-        <v>-4.927786398418722</v>
+        <v>-5.186270998895666</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.503983215591997</v>
       </c>
       <c r="E57">
-        <v>-11.40239518117749</v>
+        <v>-10.90738638300515</v>
       </c>
       <c r="F57">
-        <v>4.316373050152474</v>
+        <v>2.455160721376821</v>
       </c>
       <c r="G57">
-        <v>-5.077956427299558</v>
+        <v>-5.722186373347264</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.718746738330252</v>
       </c>
       <c r="E58">
-        <v>-9.703706830054671</v>
+        <v>-10.66441521408003</v>
       </c>
       <c r="F58">
-        <v>4.157573362301003</v>
+        <v>2.381402887831553</v>
       </c>
       <c r="G58">
-        <v>-6.252911587551728</v>
+        <v>-5.718298974651096</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.939105224567526</v>
       </c>
       <c r="E59">
-        <v>-9.891780851688207</v>
+        <v>-9.87631844592587</v>
       </c>
       <c r="F59">
-        <v>4.220472955930375</v>
+        <v>2.229980640069415</v>
       </c>
       <c r="G59">
-        <v>-5.935546864311406</v>
+        <v>-6.231584414986924</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.170084323950694</v>
       </c>
       <c r="E60">
-        <v>-9.11924201315685</v>
+        <v>-9.189526808406923</v>
       </c>
       <c r="F60">
-        <v>3.671881673221985</v>
+        <v>2.280226093253622</v>
       </c>
       <c r="G60">
-        <v>-6.105764800907401</v>
+        <v>-6.088967270208178</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.412636222355526</v>
       </c>
       <c r="E61">
-        <v>-9.252506104936623</v>
+        <v>-8.796126325296514</v>
       </c>
       <c r="F61">
-        <v>4.200040445572922</v>
+        <v>2.307736174700593</v>
       </c>
       <c r="G61">
-        <v>-5.745234026597612</v>
+        <v>-6.577421918737928</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.668913027277809</v>
       </c>
       <c r="E62">
-        <v>-9.33044111544703</v>
+        <v>-8.603342562020622</v>
       </c>
       <c r="F62">
-        <v>3.940499684397392</v>
+        <v>2.00473594610459</v>
       </c>
       <c r="G62">
-        <v>-6.059967119290092</v>
+        <v>-6.78482730128974</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.936676230892234</v>
       </c>
       <c r="E63">
-        <v>-8.545779053058499</v>
+        <v>-8.439996760615115</v>
       </c>
       <c r="F63">
-        <v>3.775265238560975</v>
+        <v>1.902142643267871</v>
       </c>
       <c r="G63">
-        <v>-6.129684442851181</v>
+        <v>-6.890042919056197</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.208378944385104</v>
       </c>
       <c r="E64">
-        <v>-9.215858168206335</v>
+        <v>-7.473930733980723</v>
       </c>
       <c r="F64">
-        <v>3.67135648828861</v>
+        <v>2.060591103340555</v>
       </c>
       <c r="G64">
-        <v>-6.624757328919403</v>
+        <v>-6.969827273760618</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.477505755715793</v>
       </c>
       <c r="E65">
-        <v>-7.217229048415721</v>
+        <v>-7.483478966816504</v>
       </c>
       <c r="F65">
-        <v>3.556644170348935</v>
+        <v>2.199561332303811</v>
       </c>
       <c r="G65">
-        <v>-6.357101182693877</v>
+        <v>-7.164520940898301</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.732331082710116</v>
       </c>
       <c r="E66">
-        <v>-8.372307722443059</v>
+        <v>-7.647011662731628</v>
       </c>
       <c r="F66">
-        <v>3.732829633250362</v>
+        <v>1.984714305978926</v>
       </c>
       <c r="G66">
-        <v>-6.958593239785058</v>
+        <v>-7.188349206781392</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.959091305731326</v>
       </c>
       <c r="E67">
-        <v>-8.236630614883561</v>
+        <v>-7.567598108989581</v>
       </c>
       <c r="F67">
-        <v>3.797356140458832</v>
+        <v>1.954796988859419</v>
       </c>
       <c r="G67">
-        <v>-6.530642597154359</v>
+        <v>-7.422754909894498</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.144480373014019</v>
       </c>
       <c r="E68">
-        <v>-7.575219251770641</v>
+        <v>-7.20306244458673</v>
       </c>
       <c r="F68">
-        <v>3.567217451878268</v>
+        <v>2.074509332442392</v>
       </c>
       <c r="G68">
-        <v>-6.09446027682788</v>
+        <v>-7.018663862081984</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.274289693123391</v>
       </c>
       <c r="E69">
-        <v>-7.435679657679052</v>
+        <v>-7.692784204742563</v>
       </c>
       <c r="F69">
-        <v>3.939015250011575</v>
+        <v>1.482945662346376</v>
       </c>
       <c r="G69">
-        <v>-6.810817263694273</v>
+        <v>-7.313181959405473</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.337394503728903</v>
       </c>
       <c r="E70">
-        <v>-7.929085316280008</v>
+        <v>-6.715512813953783</v>
       </c>
       <c r="F70">
-        <v>3.375925881019389</v>
+        <v>1.988738514821726</v>
       </c>
       <c r="G70">
-        <v>-6.323733256074858</v>
+        <v>-7.256594070393093</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.327482829900918</v>
       </c>
       <c r="E71">
-        <v>-7.391177998333514</v>
+        <v>-7.182067961339722</v>
       </c>
       <c r="F71">
-        <v>3.450677755448016</v>
+        <v>1.752681969515562</v>
       </c>
       <c r="G71">
-        <v>-6.941377989951257</v>
+        <v>-6.827160524834642</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.243149858115292</v>
       </c>
       <c r="E72">
-        <v>-7.956255624767036</v>
+        <v>-7.526506236141728</v>
       </c>
       <c r="F72">
-        <v>3.422056004946488</v>
+        <v>1.997994692180607</v>
       </c>
       <c r="G72">
-        <v>-6.508819383117244</v>
+        <v>-7.314176653094687</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.087278035757976</v>
       </c>
       <c r="E73">
-        <v>-7.683497624220246</v>
+        <v>-7.076136153288645</v>
       </c>
       <c r="F73">
-        <v>3.171406939472608</v>
+        <v>1.876521239499282</v>
       </c>
       <c r="G73">
-        <v>-5.840505318216518</v>
+        <v>-6.798108159024733</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.868495001309909</v>
       </c>
       <c r="E74">
-        <v>-9.189090721217816</v>
+        <v>-7.095361368511276</v>
       </c>
       <c r="F74">
-        <v>3.281101007686124</v>
+        <v>1.704381522993128</v>
       </c>
       <c r="G74">
-        <v>-5.413873101604332</v>
+        <v>-6.236385574289981</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.597382008928706</v>
       </c>
       <c r="E75">
-        <v>-7.82573265246165</v>
+        <v>-8.0733761841272</v>
       </c>
       <c r="F75">
-        <v>2.973551385313946</v>
+        <v>1.608633848373145</v>
       </c>
       <c r="G75">
-        <v>-5.755750105810616</v>
+        <v>-6.151061219563217</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.285737266905103</v>
       </c>
       <c r="E76">
-        <v>-9.0477735526792</v>
+        <v>-8.480390893960397</v>
       </c>
       <c r="F76">
-        <v>2.94897538120769</v>
+        <v>1.622788990552183</v>
       </c>
       <c r="G76">
-        <v>-6.429886131149525</v>
+        <v>-6.089139579351191</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.948859527098878</v>
       </c>
       <c r="E77">
-        <v>-10.29056804988692</v>
+        <v>-8.574585726807509</v>
       </c>
       <c r="F77">
-        <v>3.187407684225083</v>
+        <v>1.462599302198814</v>
       </c>
       <c r="G77">
-        <v>-5.782055968310674</v>
+        <v>-6.003026779757911</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.598848263893458</v>
       </c>
       <c r="E78">
-        <v>-8.87043142910902</v>
+        <v>-8.610789269926039</v>
       </c>
       <c r="F78">
-        <v>3.129975315454188</v>
+        <v>1.545969511086168</v>
       </c>
       <c r="G78">
-        <v>-4.986687407138829</v>
+        <v>-5.495038540197452</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.24426057287625</v>
       </c>
       <c r="E79">
-        <v>-10.19164686255215</v>
+        <v>-9.751501985980797</v>
       </c>
       <c r="F79">
-        <v>2.869248332157849</v>
+        <v>1.792122198297652</v>
       </c>
       <c r="G79">
-        <v>-4.669706463353401</v>
+        <v>-5.156346644392326</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.891784879628067</v>
       </c>
       <c r="E80">
-        <v>-10.58084429580183</v>
+        <v>-9.456030072698521</v>
       </c>
       <c r="F80">
-        <v>3.317267528492351</v>
+        <v>1.381091263232954</v>
       </c>
       <c r="G80">
-        <v>-5.215425183744628</v>
+        <v>-5.230309038658565</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.540736786144557</v>
       </c>
       <c r="E81">
-        <v>-11.90875470590059</v>
+        <v>-10.81731153579227</v>
       </c>
       <c r="F81">
-        <v>2.696987674010886</v>
+        <v>1.558958311962064</v>
       </c>
       <c r="G81">
-        <v>-4.309512475095865</v>
+        <v>-4.774373824755723</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.191561039124393</v>
       </c>
       <c r="E82">
-        <v>-12.62446515387432</v>
+        <v>-11.69253021790736</v>
       </c>
       <c r="F82">
-        <v>3.244805261565061</v>
+        <v>1.469395228371381</v>
       </c>
       <c r="G82">
-        <v>-3.261332461443565</v>
+        <v>-4.173638883595965</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.845639078911652</v>
       </c>
       <c r="E83">
-        <v>-12.8833721946528</v>
+        <v>-12.37180454292837</v>
       </c>
       <c r="F83">
-        <v>2.620411734561294</v>
+        <v>1.264478670471256</v>
       </c>
       <c r="G83">
-        <v>-4.251595717086608</v>
+        <v>-4.149126602630003</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.50146194220051</v>
       </c>
       <c r="E84">
-        <v>-14.21482944722296</v>
+        <v>-13.7070702902834</v>
       </c>
       <c r="F84">
-        <v>3.135624781141281</v>
+        <v>1.413125887434016</v>
       </c>
       <c r="G84">
-        <v>-3.63784621414015</v>
+        <v>-3.658807882462198</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.165573587196845</v>
       </c>
       <c r="E85">
-        <v>-15.50512422235274</v>
+        <v>-14.29023930524787</v>
       </c>
       <c r="F85">
-        <v>3.060293049530693</v>
+        <v>1.223722994253521</v>
       </c>
       <c r="G85">
-        <v>-4.16349614085949</v>
+        <v>-3.901614961669507</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.8444656456646039</v>
       </c>
       <c r="E86">
-        <v>-16.04085525756503</v>
+        <v>-15.54593783004183</v>
       </c>
       <c r="F86">
-        <v>2.332134908182649</v>
+        <v>1.330154951634812</v>
       </c>
       <c r="G86">
-        <v>-3.485796449153712</v>
+        <v>-3.536131604870376</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.5464419318990215</v>
       </c>
       <c r="E87">
-        <v>-18.47744881798146</v>
+        <v>-16.58418251629042</v>
       </c>
       <c r="F87">
-        <v>3.067127080603789</v>
+        <v>1.261034318810416</v>
       </c>
       <c r="G87">
-        <v>-2.793163298386766</v>
+        <v>-3.49139649630165</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.2844790556225151</v>
       </c>
       <c r="E88">
-        <v>-19.78406986682915</v>
+        <v>-17.20766675358501</v>
       </c>
       <c r="F88">
-        <v>2.665295993914583</v>
+        <v>1.143891570910927</v>
       </c>
       <c r="G88">
-        <v>-2.867673949017139</v>
+        <v>-3.332710218564602</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.06941952166954399</v>
       </c>
       <c r="E89">
-        <v>-20.62651555838002</v>
+        <v>-19.46617891881544</v>
       </c>
       <c r="F89">
-        <v>2.564452203032577</v>
+        <v>1.131353401902153</v>
       </c>
       <c r="G89">
-        <v>-1.639441323894121</v>
+        <v>-2.881257653124702</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.08699830766908137</v>
       </c>
       <c r="E90">
-        <v>-22.94196825087385</v>
+        <v>-21.10128575776647</v>
       </c>
       <c r="F90">
-        <v>2.769875721783215</v>
+        <v>1.159736582591676</v>
       </c>
       <c r="G90">
-        <v>-2.421576020733613</v>
+        <v>-2.631200536187871</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.1742025999452037</v>
       </c>
       <c r="E91">
-        <v>-24.71278126986365</v>
+        <v>-23.20014847967049</v>
       </c>
       <c r="F91">
-        <v>2.530553752175215</v>
+        <v>1.18636859459168</v>
       </c>
       <c r="G91">
-        <v>-2.16900475675554</v>
+        <v>-2.450338593893907</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.1850267963348408</v>
       </c>
       <c r="E92">
-        <v>-26.32395730516101</v>
+        <v>-24.51777553852897</v>
       </c>
       <c r="F92">
-        <v>2.536559415845511</v>
+        <v>1.134390196800816</v>
       </c>
       <c r="G92">
-        <v>-2.67575289263522</v>
+        <v>-2.925441894584703</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.1149796581309076</v>
       </c>
       <c r="E93">
-        <v>-27.79482540227168</v>
+        <v>-26.93869903261683</v>
       </c>
       <c r="F93">
-        <v>2.388248516048288</v>
+        <v>1.220566914448855</v>
       </c>
       <c r="G93">
-        <v>-2.073754351093362</v>
+        <v>-2.64960628555522</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.03315329641852366</v>
       </c>
       <c r="E94">
-        <v>-29.44582450435716</v>
+        <v>-28.84393904255735</v>
       </c>
       <c r="F94">
-        <v>2.444627201482823</v>
+        <v>1.379411334140077</v>
       </c>
       <c r="G94">
-        <v>-1.893665189198368</v>
+        <v>-2.861870263791094</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.2518513389878446</v>
       </c>
       <c r="E95">
-        <v>-31.18186891474116</v>
+        <v>-31.86387189960258</v>
       </c>
       <c r="F95">
-        <v>2.003678949298618</v>
+        <v>1.142816350022093</v>
       </c>
       <c r="G95">
-        <v>-1.987417027465246</v>
+        <v>-3.245673215386068</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.5288860220830336</v>
       </c>
       <c r="E96">
-        <v>-35.16454107614959</v>
+        <v>-33.67329317106798</v>
       </c>
       <c r="F96">
-        <v>2.131751176710643</v>
+        <v>1.326028025234065</v>
       </c>
       <c r="G96">
-        <v>-2.424001402458757</v>
+        <v>-3.533285893266063</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.8446824631319007</v>
       </c>
       <c r="E97">
-        <v>-36.57857455288565</v>
+        <v>-36.27826207180428</v>
       </c>
       <c r="F97">
-        <v>2.18816299684129</v>
+        <v>1.104549089482367</v>
       </c>
       <c r="G97">
-        <v>-2.893943261092921</v>
+        <v>-3.719826205045698</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.182952542585924</v>
       </c>
       <c r="E98">
-        <v>-39.99415685697368</v>
+        <v>-38.70328686207541</v>
       </c>
       <c r="F98">
-        <v>1.827367574551965</v>
+        <v>1.176530903316033</v>
       </c>
       <c r="G98">
-        <v>-3.424381293392363</v>
+        <v>-3.965747902550205</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.516562344947859</v>
       </c>
       <c r="E99">
-        <v>-42.97159405574326</v>
+        <v>-40.90233542416262</v>
       </c>
       <c r="F99">
-        <v>1.589791803429067</v>
+        <v>1.241975241606805</v>
       </c>
       <c r="G99">
-        <v>-3.561158202520788</v>
+        <v>-3.811056064037561</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.831677022626305</v>
       </c>
       <c r="E100">
-        <v>-44.5728646820309</v>
+        <v>-43.52901523709946</v>
       </c>
       <c r="F100">
-        <v>1.693299623878477</v>
+        <v>1.011389234628729</v>
       </c>
       <c r="G100">
-        <v>-3.816233170561738</v>
+        <v>-4.040976507943134</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.097373634377129</v>
       </c>
       <c r="E101">
-        <v>-46.37390165813431</v>
+        <v>-45.90969411344973</v>
       </c>
       <c r="F101">
-        <v>1.624944402534267</v>
+        <v>0.7952731494427548</v>
       </c>
       <c r="G101">
-        <v>-3.831153575899951</v>
+        <v>-4.351206066215944</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.317776341238695</v>
       </c>
       <c r="E102">
-        <v>-49.40290201380447</v>
+        <v>-48.75741925442509</v>
       </c>
       <c r="F102">
-        <v>1.272792165725752</v>
+        <v>0.761475759408535</v>
       </c>
       <c r="G102">
-        <v>-4.223193426679886</v>
+        <v>-4.860679819448746</v>
       </c>
     </row>
   </sheetData>
